--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2020_T3_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2020_T3_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>76</t>
+    <t>70</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.379</t>
-  </si>
-  <si>
-    <t>(0.209)</t>
-  </si>
-  <si>
-    <t>7.842</t>
-  </si>
-  <si>
-    <t>(0.990)</t>
-  </si>
-  <si>
-    <t>7.429</t>
-  </si>
-  <si>
-    <t>(4.389)</t>
-  </si>
-  <si>
-    <t>22.170</t>
-  </si>
-  <si>
-    <t>(9.124)</t>
-  </si>
-  <si>
-    <t>1.419</t>
-  </si>
-  <si>
-    <t>(0.191)</t>
-  </si>
-  <si>
-    <t>8.368</t>
-  </si>
-  <si>
-    <t>(0.913)</t>
-  </si>
-  <si>
-    <t>11.552</t>
-  </si>
-  <si>
-    <t>(5.011)</t>
-  </si>
-  <si>
-    <t>0.391</t>
-  </si>
-  <si>
-    <t>(0.067)</t>
-  </si>
-  <si>
-    <t>16.837</t>
-  </si>
-  <si>
-    <t>(3.953)</t>
-  </si>
-  <si>
-    <t>25.497</t>
-  </si>
-  <si>
-    <t>(15.500)</t>
+    <t>1.294</t>
+  </si>
+  <si>
+    <t>(0.160)</t>
+  </si>
+  <si>
+    <t>8.443</t>
+  </si>
+  <si>
+    <t>(1.043)</t>
+  </si>
+  <si>
+    <t>2.431</t>
+  </si>
+  <si>
+    <t>(0.508)</t>
+  </si>
+  <si>
+    <t>8.784</t>
+  </si>
+  <si>
+    <t>(1.845)</t>
+  </si>
+  <si>
+    <t>1.338</t>
+  </si>
+  <si>
+    <t>(0.131)</t>
+  </si>
+  <si>
+    <t>9.014</t>
+  </si>
+  <si>
+    <t>(0.951)</t>
+  </si>
+  <si>
+    <t>3.311</t>
+  </si>
+  <si>
+    <t>(1.456)</t>
+  </si>
+  <si>
+    <t>0.410</t>
+  </si>
+  <si>
+    <t>(0.071)</t>
+  </si>
+  <si>
+    <t>11.108</t>
+  </si>
+  <si>
+    <t>(2.357)</t>
+  </si>
+  <si>
+    <t>6.536</t>
+  </si>
+  <si>
+    <t>(1.367)</t>
   </si>
   <si>
     <t>40</t>
@@ -198,7 +198,7 @@
     <t>(1.161)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.231</t>
-  </si>
-  <si>
-    <t>1.908</t>
-  </si>
-  <si>
-    <t>-4.037</t>
-  </si>
-  <si>
-    <t>-13.754</t>
-  </si>
-  <si>
-    <t>-0.270</t>
-  </si>
-  <si>
-    <t>-0.193</t>
-  </si>
-  <si>
-    <t>-9.563</t>
-  </si>
-  <si>
-    <t>-0.117</t>
-  </si>
-  <si>
-    <t>-6.324</t>
-  </si>
-  <si>
-    <t>-18.688</t>
+    <t>0.316</t>
+  </si>
+  <si>
+    <t>1.307</t>
+  </si>
+  <si>
+    <t>0.961</t>
+  </si>
+  <si>
+    <t>-0.368</t>
+  </si>
+  <si>
+    <t>-0.188</t>
+  </si>
+  <si>
+    <t>-0.839</t>
+  </si>
+  <si>
+    <t>-1.322</t>
+  </si>
+  <si>
+    <t>-0.135</t>
+  </si>
+  <si>
+    <t>-0.595</t>
+  </si>
+  <si>
+    <t>0.273</t>
   </si>
 </sst>
 </file>
